--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -513,7 +513,11 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr"/>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>用地面积</t>
+        </is>
+      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>site_area</t>
@@ -531,7 +535,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr"/>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>容积率上限（无量纲系数，中国常见 0.5–4.0）</t>
+        </is>
+      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>far_max</t>
@@ -549,7 +557,11 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>建筑密度上限（小数，0.30 = 30%）</t>
+        </is>
+      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>density_max</t>
@@ -567,7 +579,11 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>建筑限高上限</t>
+        </is>
+      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>height_max</t>
@@ -585,10 +601,36 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>建筑气候分区</t>
+        </is>
+      </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
           <t>climate_zone</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>抗震设防烈度</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>抗震设防烈度（浙江全省最高为 7 度 0.10g）</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>seismic_intensity</t>
         </is>
       </c>
     </row>
@@ -596,7 +638,7 @@
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【用地面积】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
@@ -615,6 +657,9 @@
     </dataValidation>
     <dataValidation sqref="B7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【气候分区】必须是下列之一：严寒, 寒冷, 夏热冬冷, 夏热冬暖, 温和" type="list">
       <formula1>"严寒","寒冷","夏热冬冷","夏热冬暖","温和"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【抗震设防烈度】必须是下列之一：6度(0.05g), 7度(0.10g)" type="list">
+      <formula1>"6度(0.05g)","7度(0.10g)"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -627,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -868,217 +913,302 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>【结构与造价】</t>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>采光系数</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>daylight_factor</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>总建筑面积</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
-      <c r="H14" s="5" t="n"/>
+          <t>日照时数</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>gfa</t>
+          <t>sunlight_hours</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>基底面积</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>footprint</t>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>【结构与造价】</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>楼栋数</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>栋</t>
-        </is>
-      </c>
+          <t>总建筑面积</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="n"/>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+      <c r="H16" s="5" t="n"/>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>gfa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>层数</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
+          <t>基底面积</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>floors</t>
+          <t>footprint</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>外表面积</t>
+          <t>楼栋数</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>栋</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>envelope_area</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>建筑体积</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>m³</t>
-        </is>
-      </c>
+          <t>层数</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>层</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+      <c r="H19" s="5" t="n"/>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>floors</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>【施工与安全】</t>
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>外表面积</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>envelope_area</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>标准层重复率</t>
+          <t>建筑体积</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>std_floor_repeat</t>
+          <t>volume</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>预制构件种类</t>
+          <t>楼板厚度</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>component_types</t>
+          <t>slab_thickness</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>风险特征</t>
+          <t>结构设计工作年限</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>年</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>risk_features</t>
+          <t>design_working_life</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>【绿色低碳】</t>
+          <t>【施工与安全】</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>标准层重复率</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>std_floor_repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>预制构件种类</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>component_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>风险特征</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>risk_features</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
           <t>预估装配率</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>绿地率</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>green_ratio</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A24:H24"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A6:H6"/>
   </mergeCells>
-  <dataValidations count="16">
+  <dataValidations count="21">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1106,39 +1236,59 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C15:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C16:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C17:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C13:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【采光系数】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【日照时数】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C16:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C17:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C23:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1102,99 +1102,116 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>最小平面宽度</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>min_plan_width</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>【施工与安全】</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>标准层重复率</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>预制构件种类</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>component_types</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>预制构件种类</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>component_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>风险特征</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>risk_features</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>【绿色低碳】</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>预估装配率</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>prefab_ratio_est</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1202,13 +1219,13 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A25:H25"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
     <mergeCell ref="A6:H6"/>
   </mergeCells>
-  <dataValidations count="21">
+  <dataValidations count="22">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1276,19 +1293,23 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C24:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C27:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -766,88 +766,88 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>总户数</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="inlineStr">
-        <is>
-          <t>户</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
-      <c r="H4" s="5" t="n"/>
+          <t>MiC 体系类型</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>units</t>
+          <t>mic_system</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
+          <t>总户数</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>户</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n"/>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+      <c r="H5" s="5" t="n"/>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>户型配比</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>户</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>unit_mix</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
         <is>
           <t>【居住品质】</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>层高</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>floor_height</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
         <is>
-          <t>得房率</t>
+          <t>层高</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>inner_area_ratio</t>
+          <t>floor_height</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>南向比例</t>
+          <t>得房率</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -857,14 +857,14 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>south_room_ratio</t>
+          <t>inner_area_ratio</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>窗地比</t>
+          <t>南向比例</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -874,14 +874,14 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>window_floor_ratio</t>
+          <t>south_room_ratio</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>窗墙比</t>
+          <t>窗地比</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -891,278 +891,278 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>window_wall_ratio</t>
+          <t>window_floor_ratio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>电梯数/单元</t>
+          <t>窗墙比</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>elevators_per_unit</t>
+          <t>window_wall_ratio</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>采光系数</t>
+          <t>电梯数/单元</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>台</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>daylight_factor</t>
+          <t>elevators_per_unit</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
+          <t>采光系数</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>daylight_factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
           <t>日照时数</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>sunlight_hours</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>【结构与造价】</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>总建筑面积</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="n"/>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
-      <c r="H16" s="5" t="n"/>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>gfa</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>基底面积</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
+          <t>总建筑面积</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+      <c r="H17" s="5" t="n"/>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>footprint</t>
+          <t>gfa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>楼栋数</t>
+          <t>基底面积</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>栋</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>footprint</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>层数</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+          <t>楼栋数</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>栋</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>floors</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>外表面积</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>层数</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>层</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>envelope_area</t>
+          <t>floors</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>建筑体积</t>
+          <t>外表面积</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>envelope_area</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>楼板厚度</t>
+          <t>建筑体积</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>slab_thickness</t>
+          <t>volume</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>结构设计工作年限</t>
+          <t>楼板厚度</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>design_working_life</t>
+          <t>slab_thickness</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
+          <t>结构设计工作年限</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>design_working_life</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
           <t>最小平面宽度</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>min_plan_width</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>【施工与安全】</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>标准层重复率</t>
+          <t>混凝土强度等级</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>std_floor_repeat</t>
+          <t>concrete_grade</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>预制构件种类</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>种</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>component_types</t>
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>【施工与安全】</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>风险特征</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
@@ -1172,46 +1172,80 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>risk_features</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>【绿色低碳】</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>预制构件种类</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>component_types</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>风险特征</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>risk_features</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>预估装配率</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>prefab_ratio_est</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1219,97 +1253,104 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A29:H29"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A27:H27"/>
+    <mergeCell ref="A31:H31"/>
   </mergeCells>
-  <dataValidations count="22">
+  <dataValidations count="24">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
-    <dataValidation sqref="C4:H4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总户数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C7:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层高】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C8:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【得房率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C9:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【南向比例】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C10:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【窗地比】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C12:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【电梯数/单元】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C13:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【采光系数】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【日照时数】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C16:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C17:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C23:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C24:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C27:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C4:H4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【MiC 体系类型】必须是下列之一：模块化框架结构, 模块化全预制剪力墙结构, 模块化叠合剪力墙结构, 模块化箱模框架结构, 模块化箱模框架-剪力墙结构, 模块化箱模剪力墙结构" type="list">
+      <formula1>"模块化框架结构","模块化全预制剪力墙结构","模块化叠合剪力墙结构","模块化箱模框架结构","模块化箱模框架-剪力墙结构","模块化箱模剪力墙结构"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C5:H5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总户数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C8:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层高】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C9:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【得房率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C10:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【南向比例】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C11:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【窗地比】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C13:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【电梯数/单元】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【采光系数】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C15:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【日照时数】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C17:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C23:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C24:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【混凝土强度等级】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C28:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C32:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1153,99 +1153,116 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>超限不规则项</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>irregularity_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
         <is>
           <t>【施工与安全】</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>标准层重复率</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>预制构件种类</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>component_types</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t>预制构件种类</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>component_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
           <t>风险特征</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
         <is>
           <t>risk_features</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
         <is>
           <t>【绿色低碳】</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>预估装配率</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>prefab_ratio_est</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1256,8 +1273,8 @@
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A27:H27"/>
-    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A28:H28"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
   <dataValidations count="24">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
@@ -1338,19 +1355,19 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C28:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C32:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -821,50 +821,50 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>自定义字段</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>custom</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>【居住品质】</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>层高</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>floor_height</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>得房率</t>
+          <t>层高</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>inner_area_ratio</t>
+          <t>floor_height</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>南向比例</t>
+          <t>得房率</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
@@ -874,14 +874,14 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>south_room_ratio</t>
+          <t>inner_area_ratio</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>窗地比</t>
+          <t>南向比例</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
@@ -891,14 +891,14 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>window_floor_ratio</t>
+          <t>south_room_ratio</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>窗墙比</t>
+          <t>窗地比</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -908,361 +908,378 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>window_wall_ratio</t>
+          <t>window_floor_ratio</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>电梯数/单元</t>
+          <t>窗墙比</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>台</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>elevators_per_unit</t>
+          <t>window_wall_ratio</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>采光系数</t>
+          <t>电梯数/单元</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>台</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>daylight_factor</t>
+          <t>elevators_per_unit</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
+          <t>采光系数</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>daylight_factor</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
           <t>日照时数</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>sunlight_hours</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>【结构与造价】</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>总建筑面积</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
-      <c r="H17" s="5" t="n"/>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>gfa</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>基底面积</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
+          <t>总建筑面积</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>m²</t>
         </is>
       </c>
+      <c r="C18" s="5" t="n"/>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+      <c r="H18" s="5" t="n"/>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>footprint</t>
+          <t>gfa</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>楼栋数</t>
+          <t>基底面积</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>栋</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>footprint</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>层数</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
+          <t>楼栋数</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>栋</t>
+        </is>
+      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>floors</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>外表面积</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>层数</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>层</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+      <c r="H21" s="5" t="n"/>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>envelope_area</t>
+          <t>floors</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>建筑体积</t>
+          <t>外表面积</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>envelope_area</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>楼板厚度</t>
+          <t>建筑体积</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>slab_thickness</t>
+          <t>volume</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>结构设计工作年限</t>
+          <t>楼板厚度</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>design_working_life</t>
+          <t>slab_thickness</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>最小平面宽度</t>
+          <t>结构设计工作年限</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>年</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>min_plan_width</t>
+          <t>design_working_life</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>混凝土强度等级</t>
+          <t>最小平面宽度</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>concrete_grade</t>
+          <t>min_plan_width</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
+          <t>混凝土强度等级</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>concrete_grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
           <t>超限不规则项</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>irregularity_items</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
         <is>
           <t>【施工与安全】</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>标准层重复率</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>预制构件种类</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>component_types</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>预制构件种类</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>component_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
           <t>风险特征</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
         <is>
           <t>risk_features</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>【绿色低碳】</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>预估装配率</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>prefab_ratio_est</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1270,11 +1287,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A29:H29"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A17:H17"/>
   </mergeCells>
   <dataValidations count="24">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
@@ -1287,87 +1304,87 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C8:H8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层高】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C9:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【得房率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C10:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【南向比例】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C11:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【窗地比】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C13:H13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【电梯数/单元】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【采光系数】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C15:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【日照时数】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C17:H17" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C23:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C24:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【混凝土强度等级】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C9:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层高】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C10:H10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【得房率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C11:H11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【南向比例】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C12:H12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【窗地比】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C14:H14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【电梯数/单元】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C15:H15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【采光系数】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C16:H16" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【日照时数】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C23:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C24:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C27:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【混凝土强度等级】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1228,41 +1228,109 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>【绿色低碳】</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>基坑开挖深度</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>excavation_depth</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>预估装配率</t>
+          <t>模板支撑高度</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>prefab_ratio_est</t>
+          <t>formwork_height</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
+          <t>脚手架形式</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>scaffold_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>脚手架搭设高度</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>scaffold_height</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1274,9 +1342,9 @@
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A28:H28"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A36:H36"/>
   </mergeCells>
-  <dataValidations count="24">
+  <dataValidations count="28">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1363,11 +1431,26 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C32:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
+      <formula1>"落地式钢管脚手架","附着式升降脚手架","悬挑式脚手架"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C37:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C38:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1189,7 +1189,7 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>超限不规则项</t>
+          <t>基础形式</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
@@ -1199,21 +1199,31 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>irregularity_items</t>
+          <t>foundation_type</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>【施工与安全】</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>地基基础工作年限</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>foundation_working_life</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>标准层重复率</t>
+          <t>超限不规则项</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1223,31 +1233,21 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>std_floor_repeat</t>
+          <t>irregularity_items</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>预制构件种类</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>种</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>component_types</t>
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>【施工与安全】</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>风险特征</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1257,65 +1257,65 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>risk_features</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>基坑开挖深度</t>
+          <t>预制构件种类</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>种</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>excavation_depth</t>
+          <t>component_types</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>模板支撑高度</t>
+          <t>风险特征</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>formwork_height</t>
+          <t>risk_features</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>脚手架形式</t>
+          <t>基坑开挖深度</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>scaffold_type</t>
+          <t>excavation_depth</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>脚手架搭设高度</t>
+          <t>模板支撑高度</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
@@ -1325,46 +1325,114 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>scaffold_height</t>
+          <t>formwork_height</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>【绿色低碳】</t>
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>脚手架形式</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>scaffold_type</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>预估装配率</t>
+          <t>脚手架搭设高度</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>prefab_ratio_est</t>
+          <t>scaffold_height</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
+          <t>基坑支护形式</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>retaining_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>支护混凝土强度等级</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>retaining_concrete_grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1373,12 +1441,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A30:H30"/>
     <mergeCell ref="A7:H7"/>
-    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A32:H32"/>
   </mergeCells>
-  <dataValidations count="30">
+  <dataValidations count="34">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1465,34 +1533,48 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C32:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
+    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【基础形式】必须是下列之一：筏形基础, 桩筏基础, 独立基础, 条形基础, 桩基础" type="list">
+      <formula1>"筏形基础","桩筏基础","独立基础","条形基础","桩基础"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【地基基础工作年限】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C37:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C38:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
       <formula1>"落地式钢管脚手架","附着式升降脚手架","悬挑式脚手架"</formula1>
     </dataValidation>
-    <dataValidation sqref="C37:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C39:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C40:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C39:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C40:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【基坑支护形式】必须是下列之一：排桩, 地下连续墙, 土钉墙, 放坡开挖, 其他" type="list">
+      <formula1>"排桩","地下连续墙","土钉墙","放坡开挖","其他"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C41:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【支护混凝土强度等级】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C43:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C44:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1223,7 +1223,7 @@
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>超限不规则项</t>
+          <t>钢结构体系</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
@@ -1233,21 +1233,31 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>irregularity_items</t>
+          <t>steel_system</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>【施工与安全】</t>
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>是否设地下室</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>has_basement</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>标准层重复率</t>
+          <t>超限不规则项</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
@@ -1257,31 +1267,21 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>std_floor_repeat</t>
+          <t>irregularity_items</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>预制构件种类</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>种</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>component_types</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>【施工与安全】</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>风险特征</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1291,65 +1291,65 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>risk_features</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>基坑开挖深度</t>
+          <t>预制构件种类</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>种</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>excavation_depth</t>
+          <t>component_types</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>模板支撑高度</t>
+          <t>风险特征</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>formwork_height</t>
+          <t>risk_features</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>脚手架形式</t>
+          <t>基坑开挖深度</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>scaffold_type</t>
+          <t>excavation_depth</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>脚手架搭设高度</t>
+          <t>模板支撑高度</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
@@ -1359,14 +1359,14 @@
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>scaffold_height</t>
+          <t>formwork_height</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>基坑支护形式</t>
+          <t>脚手架形式</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -1376,63 +1376,148 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>retaining_type</t>
+          <t>scaffold_type</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>支护混凝土强度等级</t>
+          <t>脚手架搭设高度</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>retaining_concrete_grade</t>
+          <t>scaffold_height</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>【绿色低碳】</t>
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>基坑支护形式</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>retaining_type</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>预估装配率</t>
+          <t>支护混凝土强度等级</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MPa</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>prefab_ratio_est</t>
+          <t>retaining_concrete_grade</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
+          <t>基坑工作年限</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>excavation_working_life</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>内支撑 / 锚拉体系</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>brace_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>锚杆自由段长度</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>anchor_free_length</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1443,10 +1528,10 @@
     <mergeCell ref="A18:H18"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A42:H42"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A47:H47"/>
+    <mergeCell ref="A34:H34"/>
   </mergeCells>
-  <dataValidations count="34">
+  <dataValidations count="38">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1540,41 +1625,55 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C37:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C38:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
+    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【钢结构体系】必须是下列之一：框架, 框架-中心支撑, 框架-偏心支撑（延性墙板）, 筒体和巨型框架" type="list">
+      <formula1>"框架","框架-中心支撑","框架-偏心支撑（延性墙板）","筒体和巨型框架"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C38:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C39:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C40:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
       <formula1>"落地式钢管脚手架","附着式升降脚手架","悬挑式脚手架"</formula1>
     </dataValidation>
-    <dataValidation sqref="C39:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C40:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【基坑支护形式】必须是下列之一：排桩, 地下连续墙, 土钉墙, 放坡开挖, 其他" type="list">
+    <dataValidation sqref="C41:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C42:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【基坑支护形式】必须是下列之一：排桩, 地下连续墙, 土钉墙, 放坡开挖, 其他" type="list">
       <formula1>"排桩","地下连续墙","土钉墙","放坡开挖","其他"</formula1>
     </dataValidation>
-    <dataValidation sqref="C41:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【支护混凝土强度等级】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C43:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C44:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C43:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【支护混凝土强度等级】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C44:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑工作年限】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C45:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【内支撑 / 锚拉体系】必须是下列之一：混凝土内支撑, 钢支撑, 锚杆（锚拉）, 无内支撑与锚拉" type="list">
+      <formula1>"混凝土内支撑","钢支撑","锚杆（锚拉）","无内支撑与锚拉"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C46:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【锚杆自由段长度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C48:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C49:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1257,31 +1257,41 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>超限不规则项</t>
+          <t>剪力墙截面厚度</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>irregularity_items</t>
+          <t>shear_wall_thickness</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>【施工与安全】</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>框架梁截面宽度</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>frame_beam_width</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>标准层重复率</t>
+          <t>框架柱截面形状</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1291,48 +1301,48 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>std_floor_repeat</t>
+          <t>frame_column_shape</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>预制构件种类</t>
+          <t>框架柱截面尺寸</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>component_types</t>
+          <t>frame_column_size</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>风险特征</t>
+          <t>筏基底板贯通筋配筋率</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>risk_features</t>
+          <t>raft_rebar_ratio</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>基坑开挖深度</t>
+          <t>基础埋置深度</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
@@ -1342,31 +1352,31 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>excavation_depth</t>
+          <t>foundation_depth</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>模板支撑高度</t>
+          <t>是否存在错层</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>formwork_height</t>
+          <t>has_staggered_floor</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>脚手架形式</t>
+          <t>是否单跨框架</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
@@ -1376,82 +1386,72 @@
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>scaffold_type</t>
+          <t>is_single_span_frame</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>脚手架搭设高度</t>
+          <t>超限不规则项</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>scaffold_height</t>
+          <t>irregularity_items</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>基坑支护形式</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>retaining_type</t>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>【施工与安全】</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>支护混凝土强度等级</t>
+          <t>标准层重复率</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>retaining_concrete_grade</t>
+          <t>std_floor_repeat</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>基坑工作年限</t>
+          <t>预制构件种类</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>年</t>
+          <t>种</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>excavation_working_life</t>
+          <t>component_types</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>内支撑 / 锚拉体系</t>
+          <t>风险特征</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
@@ -1461,14 +1461,14 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>brace_type</t>
+          <t>risk_features</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>锚杆自由段长度</t>
+          <t>基坑开挖深度</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
@@ -1478,21 +1478,31 @@
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>anchor_free_length</t>
+          <t>excavation_depth</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>【绿色低碳】</t>
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>模板支撑高度</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>formwork_height</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>预估装配率</t>
+          <t>脚手架形式</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
@@ -1502,22 +1512,148 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>prefab_ratio_est</t>
+          <t>scaffold_type</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
+          <t>脚手架搭设高度</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>scaffold_height</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>基坑支护形式</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>retaining_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>支护混凝土强度等级</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>retaining_concrete_grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>基坑工作年限</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>excavation_working_life</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>内支撑 / 锚拉体系</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>brace_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>锚杆自由段长度</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>anchor_free_length</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="inlineStr">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1526,12 +1662,12 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A55:H55"/>
     <mergeCell ref="A7:H7"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A47:H47"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A42:H42"/>
   </mergeCells>
-  <dataValidations count="38">
+  <dataValidations count="44">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1628,52 +1764,75 @@
     <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【钢结构体系】必须是下列之一：框架, 框架-中心支撑, 框架-偏心支撑（延性墙板）, 筒体和巨型框架" type="list">
       <formula1>"框架","框架-中心支撑","框架-偏心支撑（延性墙板）","筒体和巨型框架"</formula1>
     </dataValidation>
-    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C38:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C39:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C40:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
+    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【剪力墙截面厚度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【框架梁截面宽度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【框架柱截面形状】必须是下列之一：矩形, 圆形" type="list">
+      <formula1>"矩形","圆形"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【框架柱截面尺寸】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C37:H37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【筏基底板贯通筋配筋率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C38:H38" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基础埋置深度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C43:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C44:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C46:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑开挖深度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C47:H47" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【模板支撑高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C48:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【脚手架形式】必须是下列之一：落地式钢管脚手架, 附着式升降脚手架, 悬挑式脚手架" type="list">
       <formula1>"落地式钢管脚手架","附着式升降脚手架","悬挑式脚手架"</formula1>
     </dataValidation>
-    <dataValidation sqref="C41:H41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C42:H42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【基坑支护形式】必须是下列之一：排桩, 地下连续墙, 土钉墙, 放坡开挖, 其他" type="list">
+    <dataValidation sqref="C49:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【脚手架搭设高度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C50:H50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【基坑支护形式】必须是下列之一：排桩, 地下连续墙, 土钉墙, 放坡开挖, 其他" type="list">
       <formula1>"排桩","地下连续墙","土钉墙","放坡开挖","其他"</formula1>
     </dataValidation>
-    <dataValidation sqref="C43:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【支护混凝土强度等级】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C44:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑工作年限】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C45:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【内支撑 / 锚拉体系】必须是下列之一：混凝土内支撑, 钢支撑, 锚杆（锚拉）, 无内支撑与锚拉" type="list">
+    <dataValidation sqref="C51:H51" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【支护混凝土强度等级】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C52:H52" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基坑工作年限】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C53:H53" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【内支撑 / 锚拉体系】必须是下列之一：混凝土内支撑, 钢支撑, 锚杆（锚拉）, 无内支撑与锚拉" type="list">
       <formula1>"混凝土内支撑","钢支撑","锚杆（锚拉）","无内支撑与锚拉"</formula1>
     </dataValidation>
-    <dataValidation sqref="C46:H46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【锚杆自由段长度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C48:H48" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C49:H49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C54:H54" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【锚杆自由段长度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C56:H56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C57:H57" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -634,11 +634,55 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>所在省份</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>项目所在省级行政区（两字母地区码，如 ZJ）。用于提示「所选的地方册是否与项目所在地一致」</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>province</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>适用标准册</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>适用的规则册；留空＝只用国家标准（GB）。GB 永远生效、不能去掉；加进省级地区码后，该省的地方规则才会参与评估</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>standard_packs</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <dataValidations count="6">
+  <dataValidations count="7">
     <dataValidation sqref="B3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【用地面积】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
@@ -660,6 +704,9 @@
     </dataValidation>
     <dataValidation sqref="B8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【抗震设防烈度】必须是下列之一：6度(0.05g), 7度(0.10g)" type="list">
       <formula1>"6度(0.05g)","7度(0.10g)"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【所在省份】必须是下列之一：BJ, TJ, HE, SX, NM, LN, JL, HL, SH, JS, ZJ, AH, FJ, JX, SD, HA, HB, HN, GD, GX, HI, CQ, SC, GZ, YN, XZ, SN, GS, QH, NX, XJ" type="list">
+      <formula1>"BJ","TJ","HE","SX","NM","LN","JL","HL","SH","JS","ZJ","AH","FJ","JX","SD","HA","HB","HN","GD","GX","HI","CQ","SC","GZ","YN","XZ","SN","GS","QH","NX","XJ"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -719,7 +719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1045,305 +1045,458 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>【结构与造价】</t>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>日照标准日</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>daylight_standard_day</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>总建筑面积</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
+          <t>居住空间总数</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>个</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>gfa</t>
+          <t>living_space_count</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>基底面积</t>
+          <t>满足日照空间数</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>个</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>footprint</t>
+          <t>daylight_room_count</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>楼栋数</t>
+          <t>室内净高</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>栋</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>buildings</t>
+          <t>clear_height</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>层数</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>层</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
+          <t>设新风/中央空调</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>floors</t>
+          <t>has_fresh_air</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>外表面积</t>
+          <t>设担架电梯</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>envelope_area</t>
+          <t>has_stretcher_elevator</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>建筑体积</t>
+          <t>设无障碍电梯</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>m³</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>has_accessible_elevator</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>楼板厚度</t>
+          <t>电梯总台数</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>mm</t>
+          <t>台</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>slab_thickness</t>
+          <t>total_elevators</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>结构设计工作年限</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>年</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>design_working_life</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>【结构与造价】</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>最小平面宽度</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>总建筑面积</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>min_plan_width</t>
+          <t>gfa</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>混凝土强度等级</t>
+          <t>基底面积</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>MPa</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>concrete_grade</t>
+          <t>footprint</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>超限不规则项</t>
+          <t>楼栋数</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>栋</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>irregularity_items</t>
+          <t>buildings</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>【施工与安全】</t>
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>层数</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>层</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>floors</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>标准层重复率</t>
+          <t>外表面积</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>std_floor_repeat</t>
+          <t>envelope_area</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>预制构件种类</t>
+          <t>建筑体积</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>种</t>
+          <t>m³</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>component_types</t>
+          <t>volume</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>风险特征</t>
+          <t>楼板厚度</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>risk_features</t>
+          <t>slab_thickness</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>【绿色低碳】</t>
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>结构设计工作年限</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>年</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>design_working_life</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>预估装配率</t>
+          <t>最小平面宽度</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>prefab_ratio_est</t>
+          <t>min_plan_width</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
+          <t>混凝土强度等级</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>MPa</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>concrete_grade</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>超限不规则项</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>irregularity_items</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>【施工与安全】</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>标准层重复率</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>std_floor_repeat</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>预制构件种类</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>种</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>component_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>风险特征</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>risk_features</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>【绿色低碳】</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>人均公共绿地</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>m²/人</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>per_capita_green</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>预估装配率</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>prefab_ratio_est</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
           <t>绿地率</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
         <is>
           <t>green_ratio</t>
         </is>
@@ -1351,13 +1504,13 @@
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A30:H30"/>
+    <mergeCell ref="A26:H26"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A38:H38"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A42:H42"/>
   </mergeCells>
-  <dataValidations count="26">
+  <dataValidations count="32">
     <dataValidation sqref="C3:H3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【结构体系】必须是下列之一：剪力墙, 框架-剪力墙, 框架, 钢结构, MiC" type="list">
       <formula1>"剪力墙","框架-剪力墙","框架","钢结构","MiC"</formula1>
     </dataValidation>
@@ -1404,59 +1557,82 @@
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>
-    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C22:H22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C23:H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C24:H24" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C26:H26" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C27:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C28:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【混凝土强度等级】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C32:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
-      <formula1>0</formula1>
-      <formula2>1e+308</formula2>
-    </dataValidation>
-    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
+    <dataValidation sqref="C18:H18" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="取值不合法" error="【日照标准日】必须是下列之一：大寒日, 冬至日" type="list">
+      <formula1>"大寒日","冬至日"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C19:H19" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【居住空间总数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C20:H20" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【满足日照空间数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C21:H21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【室内净高】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C25:H25" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【电梯总台数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C27:H27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【总建筑面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C28:H28" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【基底面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C29:H29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼栋数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C30:H30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【层数】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C31:H31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【外表面积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C32:H32" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【建筑体积】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C33:H33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【楼板厚度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C34:H34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【结构设计工作年限】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C35:H35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【最小平面宽度】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C36:H36" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【混凝土强度等级】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C39:H39" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【标准层重复率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C40:H40" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预制构件种类】必须是数字" type="whole" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C43:H43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【人均公共绿地】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C44:H44" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【预估装配率】必须是数字" type="decimal" operator="between">
+      <formula1>0</formula1>
+      <formula2>1e+308</formula2>
+    </dataValidation>
+    <dataValidation sqref="C45:H45" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" errorTitle="类型错误" error="【绿地率】必须是数字" type="decimal" operator="between">
       <formula1>0</formula1>
       <formula2>1e+308</formula2>
     </dataValidation>

--- a/data/schemes/方案录入模板.xlsx
+++ b/data/schemes/方案录入模板.xlsx
@@ -457,7 +457,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,28 @@
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>project_notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>暂不纳入评分的代理指标</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>本项目暂不纳入评分的代理指标；仅允许 G-05、Q-05、Q-06，不能关闭硬约束。应在案例来源与边界中记录原因、资料依据和核对人；不适用项不参与维度均值。</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>scoring_exclusions</t>
         </is>
       </c>
     </row>
